--- a/output/pdf_financials_xlsx/XGC.xlsx
+++ b/output/pdf_financials_xlsx/XGC.xlsx
@@ -1434,22 +1434,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.623543</v>
+        <v>-1.623543</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>6.297743</v>
+        <v>-6.297743</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-4.639472</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.764836</v>
+        <v>-1.764836</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>4.812653</v>
+        <v>-4.812653</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.241296</v>
+        <v>-1.241296</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-1.612697</v>
@@ -1762,22 +1762,22 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.623543</v>
+        <v>-1.623543</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>6.297743</v>
+        <v>-6.297743</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-4.639472</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.764836</v>
+        <v>-1.764836</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>4.812653</v>
+        <v>-4.812653</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.241296</v>
+        <v>-1.241296</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-1.612697</v>
@@ -1978,22 +1978,22 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.623543</v>
+        <v>-1.623543</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.297743</v>
+        <v>-6.297743</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-4.639472</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.764836</v>
+        <v>-1.764836</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4.812653</v>
+        <v>-4.812653</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.241296</v>
+        <v>-1.241296</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-1.612697</v>
@@ -2188,22 +2188,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>10.82362</v>
+        <v>-10.82362</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>48.444177</v>
+        <v>-48.444177</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>57.9934</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-58.827867</v>
+        <v>58.827867</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-68.75218599999999</v>
+        <v>68.75218599999999</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-62.0648</v>
+        <v>62.0648</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>80.63485</v>
@@ -2266,22 +2266,22 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.623543</v>
+        <v>-1.623543</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>6.297743</v>
+        <v>-6.297743</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-4.639472</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.764836</v>
+        <v>-1.764836</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.812653</v>
+        <v>-4.812653</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.241296</v>
+        <v>-1.241296</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.612697</v>
@@ -2410,22 +2410,22 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.630319</v>
+        <v>-1.616767</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>6.322004</v>
+        <v>-6.273482</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-4.601308</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.785593</v>
+        <v>-1.744079</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>4.824557</v>
+        <v>-4.800749</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.257011</v>
+        <v>-1.225581</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.608437</v>
@@ -2574,22 +2574,22 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -6246,10 +6246,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.278887</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.048507</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>0</v>
@@ -6309,46 +6309,46 @@
         <v>4.956307</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.315588</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.14644</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.387926</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.580359</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.607069</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.777359</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.750535</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>5.805432</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.841914</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.819301</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>6.03925</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.992369</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.987141</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>6.200695</v>
       </c>
     </row>
     <row r="93">
@@ -10454,7 +10454,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -12040,7 +12044,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -13624,7 +13632,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -14028,7 +14040,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -15012,7 +15028,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -16180,7 +16200,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -16984,7 +17008,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -17883,7 +17911,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -20075,7 +20107,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -56601,10 +56637,10 @@
         </is>
       </c>
       <c r="K480" s="5" t="n">
-        <v>1.241296</v>
+        <v>-1.241296</v>
       </c>
       <c r="L480" s="5" t="n">
-        <v>1.612697</v>
+        <v>-1.612697</v>
       </c>
       <c r="M480" t="inlineStr">
         <is>
@@ -58382,10 +58418,10 @@
         </is>
       </c>
       <c r="J498" s="5" t="n">
-        <v>4.812653</v>
+        <v>-4.812653</v>
       </c>
       <c r="K498" s="5" t="n">
-        <v>1.241296</v>
+        <v>-1.241296</v>
       </c>
       <c r="L498" t="inlineStr">
         <is>
@@ -59276,10 +59312,10 @@
         </is>
       </c>
       <c r="I507" s="5" t="n">
-        <v>1.764836</v>
+        <v>-1.764836</v>
       </c>
       <c r="J507" s="5" t="n">
-        <v>4.812653</v>
+        <v>-4.812653</v>
       </c>
       <c r="K507" t="inlineStr">
         <is>
@@ -62689,10 +62725,10 @@
         </is>
       </c>
       <c r="F541" s="5" t="n">
-        <v>1.623543</v>
+        <v>-1.623543</v>
       </c>
       <c r="G541" s="5" t="n">
-        <v>6.297743</v>
+        <v>-6.297743</v>
       </c>
       <c r="H541" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/XGC.xlsx
+++ b/output/pdf_financials_xlsx/XGC.xlsx
@@ -2763,34 +2763,34 @@
         <v>0.19476</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.009561</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.124923</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.036248</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.064455</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.006767</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.032671</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.033522</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.037026</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.016299</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.038293</v>
       </c>
     </row>
     <row r="35">
@@ -2883,34 +2883,34 @@
         <v>0.19476</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.009561</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.124923</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.036248</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.064455</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.006767</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.032671</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.033522</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.037026</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.016299</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.038293</v>
       </c>
     </row>
     <row r="37">
@@ -3603,34 +3603,34 @@
         <v>0.028775</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.026185</v>
+        <v>0.016624</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.128396</v>
+        <v>0.003473</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.042621</v>
+        <v>0.006373</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.07349799999999999</v>
+        <v>0.009043000000000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.01257</v>
+        <v>0.005803</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.042923</v>
+        <v>0.010252</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.064522</v>
+        <v>0.031</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.045169</v>
+        <v>0.008142999999999999</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.025488</v>
+        <v>0.009188999999999999</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.048138</v>
+        <v>0.009845</v>
       </c>
     </row>
     <row r="49">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">

--- a/output/pdf_financials_xlsx/XGC.xlsx
+++ b/output/pdf_financials_xlsx/XGC.xlsx
@@ -2022,10 +2022,8 @@
       <c r="Q23" s="3" t="n">
         <v>-0.942786</v>
       </c>
-      <c r="R23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R23" s="3" t="n">
+        <v>1.26883</v>
       </c>
     </row>
     <row r="24">
@@ -4784,13 +4782,13 @@
         <v>1.337452</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.554608</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.768835</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.949866</v>
       </c>
       <c r="O67" s="3" t="n">
         <v>0</v>
@@ -6714,10 +6712,8 @@
       <c r="Q99" s="3" t="n">
         <v>-0.942786</v>
       </c>
-      <c r="R99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R99" s="3" t="n">
+        <v>1.26883</v>
       </c>
     </row>
     <row r="100">
@@ -7395,13 +7391,13 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.108871</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.025203</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000425</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -8819,13 +8815,13 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.108871</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.025203</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000425</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -8879,13 +8875,13 @@
         <v>-1.099445</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-5.008588</v>
+        <v>-5.117459</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-4.862584</v>
+        <v>-4.887787</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.05673</v>
+        <v>-1.057155</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.837794</v>
@@ -21844,7 +21840,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -26659,7 +26659,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -28471,7 +28475,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -36241,7 +36249,11 @@
           <t>Purchase of equipment 5</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -37037,7 +37049,11 @@
           <t>Purchase of equipment 5 $</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -38263,7 +38279,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
